--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484137_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484137_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.856299999999999</v>
+        <v>10.0425</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3287</v>
+        <v>8.4308</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5275</v>
+        <v>1.6117</v>
       </c>
       <c r="G2" t="n">
         <v>9.1091</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0844</v>
+        <v>0.2706</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0567</v>
+        <v>0.1588</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0277</v>
+        <v>0.1118</v>
       </c>
       <c r="V2" t="n">
         <v>0.266</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.053100000000001</v>
+        <v>7.8056</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0835</v>
+        <v>5.4713</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9696</v>
+        <v>2.3344</v>
       </c>
       <c r="G3" t="n">
         <v>6.1217</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4653</v>
+        <v>-0.7128</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4876</v>
+        <v>-0.1246</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9529</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>1.2065</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4496</v>
+        <v>5.5134</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6871</v>
+        <v>2.8912</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7625</v>
+        <v>2.6222</v>
       </c>
       <c r="G4" t="n">
         <v>6.191</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.224</v>
+        <v>-0.1602</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.255</v>
+        <v>-0.0509</v>
       </c>
       <c r="U4" t="n">
-        <v>0.031</v>
+        <v>-0.1092</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1206</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5473</v>
+        <v>4.7846</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1437</v>
+        <v>2.8579</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4036</v>
+        <v>1.9267</v>
       </c>
       <c r="G5" t="n">
         <v>6.1464</v>
@@ -844,13 +844,13 @@
         <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0673</v>
+        <v>0.3046</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8105</v>
+        <v>-0.0963</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8778</v>
+        <v>0.4009</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6745</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9356</v>
+        <v>4.4381</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0535</v>
+        <v>1.3596</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8821</v>
+        <v>3.0785</v>
       </c>
       <c r="G6" t="n">
         <v>4.7178</v>
@@ -922,13 +922,13 @@
         <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7307</v>
+        <v>-0.2282</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8105</v>
+        <v>-0.5044</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0798</v>
+        <v>0.2762</v>
       </c>
       <c r="V6" t="n">
         <v>0.9405</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9536</v>
+        <v>2.265</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4224</v>
+        <v>0.0143</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5313</v>
+        <v>2.2507</v>
       </c>
       <c r="G7" t="n">
         <v>2.1375</v>
@@ -1000,13 +1000,13 @@
         <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7368</v>
+        <v>0.0481</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0567</v>
+        <v>-0.3514</v>
       </c>
       <c r="U7" t="n">
-        <v>0.68</v>
+        <v>0.3995</v>
       </c>
       <c r="V7" t="n">
         <v>0.6745</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.961</v>
+        <v>0.887</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.1987</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0577</v>
+        <v>1.0857</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0439</v>
@@ -1078,13 +1078,13 @@
         <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7272</v>
+        <v>0.6532</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4932</v>
+        <v>0.3911</v>
       </c>
       <c r="U8" t="n">
-        <v>0.234</v>
+        <v>0.2621</v>
       </c>
       <c r="V8" t="n">
         <v>0.6745</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8138</v>
+        <v>0.8768</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7402</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0736</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3999</v>
+        <v>1.2408</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7458</v>
+        <v>0.3171</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3459</v>
+        <v>0.9237</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2527</v>
+        <v>1.754</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3523</v>
+        <v>1.1089</v>
       </c>
       <c r="L9" t="n">
-        <v>0.605</v>
+        <v>0.6451</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6525</v>
+        <v>-0.5132</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3935</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2591</v>
+        <v>0.2786</v>
       </c>
       <c r="P9" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1359</v>
+        <v>-0.1757</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4795</v>
+        <v>0.4025</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3435</v>
+        <v>-0.5782</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1206</v>
+        <v>-0.3866</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1206</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1626</v>
+        <v>-0.2626</v>
       </c>
       <c r="E10" t="n">
-        <v>0.252</v>
+        <v>-0.2801</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.0175</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2408</v>
+        <v>-0.3999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3171</v>
+        <v>-0.7458</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9237</v>
+        <v>0.3459</v>
       </c>
       <c r="J10" t="n">
-        <v>1.754</v>
+        <v>0.2527</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1089</v>
+        <v>-0.3523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6451</v>
+        <v>0.605</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5132</v>
+        <v>-0.6525</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.3935</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2786</v>
+        <v>-0.2591</v>
       </c>
       <c r="P10" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8899</v>
+        <v>0.0595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3117</v>
+        <v>0.4592</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5782</v>
+        <v>-0.3996</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3866</v>
+        <v>-0.1206</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3866</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6239</v>
+        <v>-2.5701</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4185</v>
+        <v>-2.6106</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2054</v>
+        <v>0.0406</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3503</v>
+        <v>-1.1854</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8217</v>
+        <v>-1.5624</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5286</v>
+        <v>0.377</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4485</v>
+        <v>-0.4738</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-1.2394</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1256</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9018</v>
+        <v>-0.7116</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2477</v>
+        <v>-0.323</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6542</v>
+        <v>-0.3886</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7855</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6326000000000001</v>
+        <v>-0.4705</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7993</v>
+        <v>-0.153</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1667</v>
+        <v>-0.3175</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1206</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3271</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2026</v>
+        <v>-2.8739</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0187</v>
+        <v>-1.7246</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1839</v>
+        <v>-1.1493</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1854</v>
+        <v>-1.3503</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5624</v>
+        <v>-0.8217</v>
       </c>
       <c r="I12" t="n">
-        <v>0.377</v>
+        <v>-0.5286</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4738</v>
+        <v>-0.4485</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2394</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.1256</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7116</v>
+        <v>-0.9018</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.323</v>
+        <v>-0.2477</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3886</v>
+        <v>-0.6542</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7935</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R12" t="n">
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.103</v>
+        <v>0.3826</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5611</v>
+        <v>0.4932</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5419</v>
+        <v>-0.1106</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1206</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1206</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30.90639999999999</v>
+        <v>30.90640000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>17.1772</v>
+        <v>17.17730000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>13.7292</v>
+        <v>13.7293</v>
       </c>
       <c r="G13" t="n">
         <v>32.6848</v>
@@ -1450,13 +1450,13 @@
         <v>16.5497</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4963</v>
+        <v>5.496300000000001</v>
       </c>
       <c r="N13" t="n">
         <v>1.9324</v>
       </c>
       <c r="O13" t="n">
-        <v>3.563400000000001</v>
+        <v>3.5634</v>
       </c>
       <c r="P13" t="n">
         <v>-3.9677</v>
@@ -1468,13 +1468,13 @@
         <v>12.8951</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.02870000000000039</v>
+        <v>-0.02879999999999994</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6242</v>
+        <v>0.6242000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6529</v>
+        <v>-0.6528</v>
       </c>
       <c r="V13" t="n">
         <v>2.2185</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0132</v>
+        <v>-0.3771</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8395</v>
+        <v>0.5334</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8263</v>
+        <v>-0.9105</v>
       </c>
       <c r="G14" t="n">
         <v>-2.1081</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0436</v>
+        <v>0.6533</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6293</v>
+        <v>0.3233</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4142</v>
+        <v>0.33</v>
       </c>
       <c r="V14" t="n">
         <v>0.4826</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9459</v>
+        <v>-1.3337</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1294</v>
+        <v>-0.4828</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0753</v>
+        <v>-0.8509</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0543</v>
@@ -1624,13 +1624,13 @@
         <v>2.3806</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8242</v>
+        <v>0.4365</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1791</v>
+        <v>0.5669</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3549</v>
+        <v>-0.1304</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1206</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1769</v>
+        <v>-2.1486</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8032</v>
+        <v>1.159</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6264</v>
+        <v>-3.3076</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.3344</v>
+        <v>-0.7438</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6953</v>
+        <v>-0.1259</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6391</v>
+        <v>-0.618</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.7605</v>
+        <v>2.4626</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.4428</v>
+        <v>1.215</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3177</v>
+        <v>1.2476</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5739</v>
+        <v>-3.2064</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2525</v>
+        <v>-1.3408</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3214</v>
+        <v>-1.8655</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7527</v>
+        <v>-0.7141</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7346</v>
+        <v>-0.6291</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0181</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2065</v>
+        <v>-1.881</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>-0.6745</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4395</v>
+        <v>-2.5594</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5719</v>
+        <v>-0.7759</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8676</v>
+        <v>-1.7835</v>
       </c>
       <c r="G17" t="n">
         <v>-2.2807</v>
@@ -1780,13 +1780,13 @@
         <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3849</v>
+        <v>0.265</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3856</v>
+        <v>0.1815</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9405</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>J. MARBÀ RECASENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5669</v>
+        <v>-2.8038</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8529</v>
+        <v>0.8907</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4198</v>
+        <v>-3.6944</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7438</v>
+        <v>-2.4153</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1259</v>
+        <v>-0.222</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.618</v>
+        <v>-2.1933</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4626</v>
+        <v>0.8518</v>
       </c>
       <c r="K18" t="n">
-        <v>1.215</v>
+        <v>1.4516</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2476</v>
+        <v>-0.5999</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2064</v>
+        <v>-3.2671</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3408</v>
+        <v>-1.6736</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8655</v>
+        <v>-1.5935</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1324</v>
+        <v>-0.863</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9352</v>
+        <v>-0.1757</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1973</v>
+        <v>-0.6873</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.881</v>
+        <v>-0.1206</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6745</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARBÀ RECASENS</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2859</v>
+        <v>-2.9829</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3805</v>
+        <v>-3.7215</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6664</v>
+        <v>0.7386</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4153</v>
+        <v>-5.3344</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.222</v>
+        <v>-2.6953</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.1933</v>
+        <v>-2.6391</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8518</v>
+        <v>-3.7605</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4516</v>
+        <v>-2.4428</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5999</v>
+        <v>-1.3177</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2671</v>
+        <v>-1.5739</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6736</v>
+        <v>-0.2525</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5935</v>
+        <v>-1.3214</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.345</v>
+        <v>0.9466</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6858</v>
+        <v>0.8163</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6593</v>
+        <v>0.1303</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1206</v>
+        <v>1.2065</v>
       </c>
       <c r="W19" t="n">
         <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9233</v>
+        <v>-4.2141</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2891</v>
+        <v>-2.1871</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6342</v>
+        <v>-2.027</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4501</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2336</v>
+        <v>-0.5243</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.306</v>
+        <v>-0.2039</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.3203</v>
       </c>
       <c r="V20" t="n">
         <v>0.5538999999999999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.7207</v>
+        <v>-6.9423</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7516</v>
+        <v>-5.5975</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9691</v>
+        <v>-1.3448</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.16</v>
+        <v>-6.1379</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3182</v>
+        <v>-2.2524</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.8419</v>
+        <v>-3.8855</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.2469</v>
+        <v>-3.823</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5312</v>
+        <v>-0.9869</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.7157</v>
+        <v>-2.8362</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.9131</v>
+        <v>-2.3148</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7869</v>
+        <v>-1.2655</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.1262</v>
+        <v>-1.0493</v>
       </c>
       <c r="P21" t="n">
-        <v>2.579</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6818</v>
+        <v>0.3345</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3739</v>
+        <v>-0.0566</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3079</v>
+        <v>0.391</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4579</v>
+        <v>-0.9405</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8692</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3271</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.8605</v>
+        <v>-7.5447</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.5157</v>
+        <v>-3.5476</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3448</v>
+        <v>-3.9972</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.1379</v>
+        <v>-9.16</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2524</v>
+        <v>-2.3182</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.8855</v>
+        <v>-6.8419</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.823</v>
+        <v>-4.2469</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9869</v>
+        <v>-1.5312</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.8362</v>
+        <v>-2.7157</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3148</v>
+        <v>-4.9131</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2655</v>
+        <v>-0.7869</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0493</v>
+        <v>-4.1262</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1984</v>
+        <v>2.579</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5838</v>
+        <v>-0.5058</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9748</v>
+        <v>-0.1699</v>
       </c>
       <c r="U22" t="n">
-        <v>0.391</v>
+        <v>-0.3359</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9405</v>
+        <v>-0.4579</v>
       </c>
       <c r="W22" t="n">
-        <v>0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2065</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-30.9064</v>
+        <v>-30.9066</v>
       </c>
       <c r="E23" t="n">
-        <v>-13.7292</v>
+        <v>-13.7293</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.1771</v>
+        <v>-17.1773</v>
       </c>
       <c r="G23" t="n">
         <v>-32.6846</v>
@@ -2248,13 +2248,13 @@
         <v>16.8627</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0287999999999996</v>
+        <v>0.02869999999999995</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6529000000000004</v>
+        <v>0.6528</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6243000000000001</v>
+        <v>-0.6241</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2181</v>
@@ -2263,7 +2263,7 @@
         <v>4.0089</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.227</v>
+        <v>-6.226999999999999</v>
       </c>
     </row>
   </sheetData>
